--- a/tests/scen_results_test_2025.xlsx
+++ b/tests/scen_results_test_2025.xlsx
@@ -28,7 +28,7 @@
     <t>2.0.11</t>
   </si>
   <si>
-    <t>2025-06-12</t>
+    <t>2025-06-17</t>
   </si>
   <si>
     <t>Scenario</t>
@@ -6805,46 +6805,46 @@
         <v>0</v>
       </c>
       <c r="E116" s="3">
-        <v>42909.89790940502</v>
+        <v>47505.4691486307</v>
       </c>
       <c r="F116" s="3">
-        <v>45155.85815602836</v>
+        <v>48815.58115183246</v>
       </c>
       <c r="G116" s="3">
-        <v>36428.0866873065</v>
+        <v>48743.9154334038</v>
       </c>
       <c r="H116" s="3">
-        <v>37078.58823529412</v>
+        <v>49614.34249471459</v>
       </c>
       <c r="I116" s="3">
-        <v>37891.71517027864</v>
+        <v>50702.37632135306</v>
       </c>
       <c r="J116" s="3">
-        <v>38704.84210526316</v>
+        <v>51790.41014799155</v>
       </c>
       <c r="K116" s="3">
-        <v>39355.34365325078</v>
+        <v>52660.83720930232</v>
       </c>
       <c r="L116" s="3">
-        <v>40331.09597523219</v>
+        <v>53966.47780126851</v>
       </c>
       <c r="M116" s="3">
-        <v>41144.22291021672</v>
+        <v>55054.51162790698</v>
       </c>
       <c r="N116" s="3">
-        <v>41957.34984520124</v>
+        <v>56142.54545454546</v>
       </c>
       <c r="O116" s="3">
-        <v>42770.47678018576</v>
+        <v>57230.57928118393</v>
       </c>
       <c r="P116" s="3">
-        <v>43746.22910216718</v>
+        <v>58536.21987315011</v>
       </c>
       <c r="Q116" s="3">
-        <v>44559.35603715171</v>
+        <v>59624.25369978858</v>
       </c>
       <c r="R116" s="3">
-        <v>532033.0625669814</v>
+        <v>690387.5196450722</v>
       </c>
     </row>
     <row r="117" spans="1:18">
@@ -8335,46 +8335,46 @@
         <v>0</v>
       </c>
       <c r="E145" s="3">
-        <v>42909.89790940502</v>
+        <v>47505.4691486307</v>
       </c>
       <c r="F145" s="3">
-        <v>45155.85815602836</v>
+        <v>48815.58115183246</v>
       </c>
       <c r="G145" s="3">
-        <v>36428.0866873065</v>
+        <v>48743.9154334038</v>
       </c>
       <c r="H145" s="3">
-        <v>37078.58823529412</v>
+        <v>49614.34249471459</v>
       </c>
       <c r="I145" s="3">
-        <v>37891.71517027864</v>
+        <v>50702.37632135306</v>
       </c>
       <c r="J145" s="3">
-        <v>38704.84210526316</v>
+        <v>51790.41014799155</v>
       </c>
       <c r="K145" s="3">
-        <v>39355.34365325078</v>
+        <v>52660.83720930232</v>
       </c>
       <c r="L145" s="3">
-        <v>40331.09597523219</v>
+        <v>53966.47780126851</v>
       </c>
       <c r="M145" s="3">
-        <v>41144.22291021672</v>
+        <v>55054.51162790698</v>
       </c>
       <c r="N145" s="3">
-        <v>41957.34984520124</v>
+        <v>56142.54545454546</v>
       </c>
       <c r="O145" s="3">
-        <v>42770.47678018576</v>
+        <v>57230.57928118393</v>
       </c>
       <c r="P145" s="3">
-        <v>43746.22910216718</v>
+        <v>58536.21987315011</v>
       </c>
       <c r="Q145" s="3">
-        <v>44559.35603715171</v>
+        <v>59624.25369978858</v>
       </c>
       <c r="R145" s="3">
-        <v>532033.0625669814</v>
+        <v>690387.5196450722</v>
       </c>
     </row>
     <row r="146" spans="1:18">
@@ -9865,46 +9865,46 @@
         <v>0</v>
       </c>
       <c r="E174" s="3">
-        <v>42909.89790940502</v>
+        <v>47505.4691486307</v>
       </c>
       <c r="F174" s="3">
-        <v>45155.85815602836</v>
+        <v>48815.58115183246</v>
       </c>
       <c r="G174" s="3">
-        <v>36428.0866873065</v>
+        <v>48743.9154334038</v>
       </c>
       <c r="H174" s="3">
-        <v>37078.58823529412</v>
+        <v>49614.34249471459</v>
       </c>
       <c r="I174" s="3">
-        <v>37891.71517027864</v>
+        <v>50702.37632135306</v>
       </c>
       <c r="J174" s="3">
-        <v>38704.84210526316</v>
+        <v>51790.41014799155</v>
       </c>
       <c r="K174" s="3">
-        <v>39355.34365325078</v>
+        <v>52660.83720930232</v>
       </c>
       <c r="L174" s="3">
-        <v>40331.09597523219</v>
+        <v>53966.47780126851</v>
       </c>
       <c r="M174" s="3">
-        <v>41144.22291021672</v>
+        <v>55054.51162790698</v>
       </c>
       <c r="N174" s="3">
-        <v>41957.34984520124</v>
+        <v>56142.54545454546</v>
       </c>
       <c r="O174" s="3">
-        <v>42770.47678018576</v>
+        <v>57230.57928118393</v>
       </c>
       <c r="P174" s="3">
-        <v>43746.22910216718</v>
+        <v>58536.21987315011</v>
       </c>
       <c r="Q174" s="3">
-        <v>44559.35603715171</v>
+        <v>59624.25369978858</v>
       </c>
       <c r="R174" s="3">
-        <v>532033.0625669814</v>
+        <v>690387.5196450722</v>
       </c>
     </row>
     <row r="175" spans="1:18">
@@ -15883,46 +15883,46 @@
         <v>0</v>
       </c>
       <c r="E33" s="3">
-        <v>2421198277.24903</v>
+        <v>2680504164.922783</v>
       </c>
       <c r="F33" s="3">
-        <v>2547926965.61308</v>
+        <v>2754427457.209621</v>
       </c>
       <c r="G33" s="3">
-        <v>2055460978.187346</v>
+        <v>2750383706.875756</v>
       </c>
       <c r="H33" s="3">
-        <v>2092165638.51212</v>
+        <v>2799497701.641396</v>
       </c>
       <c r="I33" s="3">
-        <v>2138046463.918087</v>
+        <v>2860890195.098444</v>
       </c>
       <c r="J33" s="3">
-        <v>2183927289.324055</v>
+        <v>2922282688.555493</v>
       </c>
       <c r="K33" s="3">
-        <v>2220631949.64883</v>
+        <v>2971396683.321131</v>
       </c>
       <c r="L33" s="3">
-        <v>2275688940.13599</v>
+        <v>3045067675.469589</v>
       </c>
       <c r="M33" s="3">
-        <v>2321569765.541958</v>
+        <v>3106460168.926635</v>
       </c>
       <c r="N33" s="3">
-        <v>2367450590.947926</v>
+        <v>3167852662.383685</v>
       </c>
       <c r="O33" s="3">
-        <v>2413331416.353893</v>
+        <v>3229245155.840732</v>
       </c>
       <c r="P33" s="3">
-        <v>2468388406.841054</v>
+        <v>3302916147.98919</v>
       </c>
       <c r="Q33" s="3">
-        <v>2514269232.247023</v>
+        <v>3364308641.446238</v>
       </c>
       <c r="R33" s="3">
-        <v>30020055914.52039</v>
+        <v>38955233049.68069</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -16261,46 +16261,46 @@
         <v>0</v>
       </c>
       <c r="E40" s="3">
-        <v>81943894302.05118</v>
+        <v>82203200189.72493</v>
       </c>
       <c r="F40" s="3">
-        <v>82066474389.06897</v>
+        <v>82272974880.66551</v>
       </c>
       <c r="G40" s="3">
-        <v>81653133988.08789</v>
+        <v>82348056716.77629</v>
       </c>
       <c r="H40" s="3">
-        <v>82161792562.89587</v>
+        <v>82869124626.02515</v>
       </c>
       <c r="I40" s="3">
-        <v>82845077550.40295</v>
+        <v>83567921281.5833</v>
       </c>
       <c r="J40" s="3">
-        <v>83731108094.0694</v>
+        <v>84469463493.30084</v>
       </c>
       <c r="K40" s="3">
-        <v>84768854255.62154</v>
+        <v>85519618989.29384</v>
       </c>
       <c r="L40" s="3">
-        <v>86096683457.49461</v>
+        <v>86866062192.8282</v>
       </c>
       <c r="M40" s="3">
-        <v>87533172895.36378</v>
+        <v>88318063298.74846</v>
       </c>
       <c r="N40" s="3">
-        <v>89091108850.43535</v>
+        <v>89891510921.87111</v>
       </c>
       <c r="O40" s="3">
-        <v>90744251166.41216</v>
+        <v>91560164905.899</v>
       </c>
       <c r="P40" s="3">
-        <v>92525318108.40607</v>
+        <v>93359845849.55421</v>
       </c>
       <c r="Q40" s="3">
-        <v>94316405792.30682</v>
+        <v>95166445201.50604</v>
       </c>
       <c r="R40" s="3">
-        <v>1119477275412.616</v>
+        <v>1128412452547.777</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -16387,46 +16387,46 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>2421198277.24903</v>
+        <v>2680504164.922783</v>
       </c>
       <c r="F43" s="3">
-        <v>2547926965.61308</v>
+        <v>2754427457.209621</v>
       </c>
       <c r="G43" s="3">
-        <v>2055460978.187346</v>
+        <v>2750383706.875756</v>
       </c>
       <c r="H43" s="3">
-        <v>2092165638.51212</v>
+        <v>2799497701.641396</v>
       </c>
       <c r="I43" s="3">
-        <v>2138046463.918087</v>
+        <v>2860890195.098444</v>
       </c>
       <c r="J43" s="3">
-        <v>2183927289.324055</v>
+        <v>2922282688.555493</v>
       </c>
       <c r="K43" s="3">
-        <v>2220631949.64883</v>
+        <v>2971396683.321131</v>
       </c>
       <c r="L43" s="3">
-        <v>2275688940.13599</v>
+        <v>3045067675.469589</v>
       </c>
       <c r="M43" s="3">
-        <v>2321569765.541958</v>
+        <v>3106460168.926635</v>
       </c>
       <c r="N43" s="3">
-        <v>2367450590.947926</v>
+        <v>3167852662.383685</v>
       </c>
       <c r="O43" s="3">
-        <v>2413331416.353893</v>
+        <v>3229245155.840732</v>
       </c>
       <c r="P43" s="3">
-        <v>2468388406.841054</v>
+        <v>3302916147.98919</v>
       </c>
       <c r="Q43" s="3">
-        <v>2514269232.247023</v>
+        <v>3364308641.446238</v>
       </c>
       <c r="R43" s="3">
-        <v>30020055914.52039</v>
+        <v>38955233049.68069</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -16765,46 +16765,46 @@
         <v>0</v>
       </c>
       <c r="E50" s="3">
-        <v>81943894302.05118</v>
+        <v>82203200189.72493</v>
       </c>
       <c r="F50" s="3">
-        <v>82066474389.06897</v>
+        <v>82272974880.66551</v>
       </c>
       <c r="G50" s="3">
-        <v>81653133988.08789</v>
+        <v>82348056716.77629</v>
       </c>
       <c r="H50" s="3">
-        <v>82161792562.89587</v>
+        <v>82869124626.02515</v>
       </c>
       <c r="I50" s="3">
-        <v>82845077550.40295</v>
+        <v>83567921281.5833</v>
       </c>
       <c r="J50" s="3">
-        <v>83731108094.0694</v>
+        <v>84469463493.30084</v>
       </c>
       <c r="K50" s="3">
-        <v>84768854255.62154</v>
+        <v>85519618989.29384</v>
       </c>
       <c r="L50" s="3">
-        <v>86096683457.49461</v>
+        <v>86866062192.8282</v>
       </c>
       <c r="M50" s="3">
-        <v>87533172895.36378</v>
+        <v>88318063298.74846</v>
       </c>
       <c r="N50" s="3">
-        <v>89091108850.43535</v>
+        <v>89891510921.87111</v>
       </c>
       <c r="O50" s="3">
-        <v>90744251166.41216</v>
+        <v>91560164905.899</v>
       </c>
       <c r="P50" s="3">
-        <v>92525318108.40607</v>
+        <v>93359845849.55421</v>
       </c>
       <c r="Q50" s="3">
-        <v>94316405792.30682</v>
+        <v>95166445201.50604</v>
       </c>
       <c r="R50" s="3">
-        <v>1119477275412.616</v>
+        <v>1128412452547.777</v>
       </c>
     </row>
     <row r="51" spans="1:18">
@@ -16891,46 +16891,46 @@
         <v>0</v>
       </c>
       <c r="E53" s="3">
-        <v>2421198277.24903</v>
+        <v>2680504164.922783</v>
       </c>
       <c r="F53" s="3">
-        <v>2547926965.61308</v>
+        <v>2754427457.209621</v>
       </c>
       <c r="G53" s="3">
-        <v>2055460978.187346</v>
+        <v>2750383706.875756</v>
       </c>
       <c r="H53" s="3">
-        <v>2092165638.51212</v>
+        <v>2799497701.641396</v>
       </c>
       <c r="I53" s="3">
-        <v>2138046463.918087</v>
+        <v>2860890195.098444</v>
       </c>
       <c r="J53" s="3">
-        <v>2183927289.324055</v>
+        <v>2922282688.555493</v>
       </c>
       <c r="K53" s="3">
-        <v>2220631949.64883</v>
+        <v>2971396683.321131</v>
       </c>
       <c r="L53" s="3">
-        <v>2275688940.13599</v>
+        <v>3045067675.469589</v>
       </c>
       <c r="M53" s="3">
-        <v>2321569765.541958</v>
+        <v>3106460168.926635</v>
       </c>
       <c r="N53" s="3">
-        <v>2367450590.947926</v>
+        <v>3167852662.383685</v>
       </c>
       <c r="O53" s="3">
-        <v>2413331416.353893</v>
+        <v>3229245155.840732</v>
       </c>
       <c r="P53" s="3">
-        <v>2468388406.841054</v>
+        <v>3302916147.98919</v>
       </c>
       <c r="Q53" s="3">
-        <v>2514269232.247023</v>
+        <v>3364308641.446238</v>
       </c>
       <c r="R53" s="3">
-        <v>30020055914.52039</v>
+        <v>38955233049.68069</v>
       </c>
     </row>
     <row r="54" spans="1:18">
@@ -17269,46 +17269,46 @@
         <v>0</v>
       </c>
       <c r="E60" s="3">
-        <v>81943894302.05118</v>
+        <v>82203200189.72493</v>
       </c>
       <c r="F60" s="3">
-        <v>82066474389.06897</v>
+        <v>82272974880.66551</v>
       </c>
       <c r="G60" s="3">
-        <v>81653133988.08789</v>
+        <v>82348056716.77629</v>
       </c>
       <c r="H60" s="3">
-        <v>82161792562.89587</v>
+        <v>82869124626.02515</v>
       </c>
       <c r="I60" s="3">
-        <v>82845077550.40295</v>
+        <v>83567921281.5833</v>
       </c>
       <c r="J60" s="3">
-        <v>83731108094.0694</v>
+        <v>84469463493.30084</v>
       </c>
       <c r="K60" s="3">
-        <v>84768854255.62154</v>
+        <v>85519618989.29384</v>
       </c>
       <c r="L60" s="3">
-        <v>86096683457.49461</v>
+        <v>86866062192.8282</v>
       </c>
       <c r="M60" s="3">
-        <v>87533172895.36378</v>
+        <v>88318063298.74846</v>
       </c>
       <c r="N60" s="3">
-        <v>89091108850.43535</v>
+        <v>89891510921.87111</v>
       </c>
       <c r="O60" s="3">
-        <v>90744251166.41216</v>
+        <v>91560164905.899</v>
       </c>
       <c r="P60" s="3">
-        <v>92525318108.40607</v>
+        <v>93359845849.55421</v>
       </c>
       <c r="Q60" s="3">
-        <v>94316405792.30682</v>
+        <v>95166445201.50604</v>
       </c>
       <c r="R60" s="3">
-        <v>1119477275412.616</v>
+        <v>1128412452547.777</v>
       </c>
     </row>
     <row r="61" spans="1:18">
